--- a/data/trans_orig/P34B04-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P34B04-Provincia-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de días a la semana que la población realiza un entrenamiento físico deportivo, como fútbol, baloncesto, ciclismo, natación de competición, judo, kárate o similares</t>
+          <t>Número medio de días a la semana que, durante más de 30 minutos, la población realiza un entrenamiento físico deportivo, como fútbol, baloncesto, ciclismo, natación de competición, judo, kárate o similares (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,22 +677,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,68</t>
+          <t>0,37; 0,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,78</t>
+          <t>0,39; 0,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,96</t>
+          <t>0,32; 0,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,01; 0,19</t>
+          <t>0,01; 0,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -702,22 +702,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,01; 0,06</t>
+          <t>0,01; 0,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,4</t>
+          <t>0,21; 0,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,46</t>
+          <t>0,24; 0,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,54</t>
+          <t>0,18; 0,57</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,46</t>
+          <t>0,25; 0,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,55</t>
+          <t>0,2; 0,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,09</t>
+          <t>0,02; 0,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -817,17 +817,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,25</t>
+          <t>0,13; 0,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,23</t>
+          <t>0,12; 0,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,28</t>
+          <t>0,1; 0,28</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,39</t>
+          <t>0,19; 0,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,34</t>
+          <t>0,15; 0,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,04</t>
+          <t>0,01; 0,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,2</t>
+          <t>0,1; 0,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,5</t>
+          <t>0,28; 0,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,63</t>
+          <t>0,36; 0,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,64</t>
+          <t>0,25; 0,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,14</t>
+          <t>0,04; 0,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1037,17 +1037,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,31</t>
+          <t>0,18; 0,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,36</t>
+          <t>0,21; 0,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,34</t>
+          <t>0,16; 0,34</t>
         </is>
       </c>
     </row>
@@ -1117,27 +1117,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,69</t>
+          <t>0,32; 0,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,42</t>
+          <t>0,13; 0,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,72</t>
+          <t>0,27; 0,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,05</t>
+          <t>0,0; 0,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,17</t>
+          <t>0,02; 0,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1147,17 +1147,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,34</t>
+          <t>0,17; 0,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,23</t>
+          <t>0,1; 0,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,35</t>
+          <t>0,16; 0,36</t>
         </is>
       </c>
     </row>
@@ -1227,37 +1227,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,54</t>
+          <t>0,25; 0,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,44</t>
+          <t>0,18; 0,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,54</t>
+          <t>0,24; 0,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,18</t>
+          <t>0,02; 0,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,25</t>
+          <t>0,06; 0,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,24</t>
+          <t>0,05; 0,23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,32</t>
+          <t>0,14; 0,33</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,35</t>
+          <t>0,16; 0,34</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,4</t>
+          <t>0,24; 0,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,59</t>
+          <t>0,34; 0,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1357,12 +1357,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,16</t>
+          <t>0,07; 0,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,23</t>
+          <t>0,06; 0,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,35</t>
+          <t>0,16; 0,36</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,39</t>
+          <t>0,22; 0,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,3</t>
+          <t>0,16; 0,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,67</t>
+          <t>0,2; 0,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1472,12 +1472,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,12</t>
+          <t>0,05; 0,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,2</t>
+          <t>0,12; 0,21</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,37</t>
+          <t>0,19; 0,38</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,27</t>
+          <t>0,21; 0,28</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P34B04-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P34B04-Provincia-trans_orig.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,24</t>
         </is>
       </c>
     </row>
@@ -677,17 +677,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,7</t>
+          <t>0,35; 0,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 0,76</t>
+          <t>0,41; 0,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,99</t>
+          <t>0,3; 0,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -702,22 +702,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,01; 0,07</t>
+          <t>0,01; 0,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,38</t>
+          <t>0,21; 0,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,45</t>
+          <t>0,25; 0,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,57</t>
+          <t>0,15; 0,37</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,17</t>
+          <t>0,15</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,47</t>
+          <t>0,26; 0,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,42</t>
+          <t>0,24; 0,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,52</t>
+          <t>0,18; 0,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,08</t>
+          <t>0,01; 0,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -822,12 +822,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,22</t>
+          <t>0,13; 0,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,28</t>
+          <t>0,1; 0,24</t>
         </is>
       </c>
     </row>
@@ -854,29 +854,29 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>0,14</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,03</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,01</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,08</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
           <t>0,15</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,03</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,08</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,15</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0,12</t>
@@ -884,7 +884,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,12</t>
+          <t>0,11</t>
         </is>
       </c>
     </row>
@@ -897,17 +897,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,4</t>
+          <t>0,18; 0,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,34</t>
+          <t>0,15; 0,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,27</t>
+          <t>0,07; 0,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -922,22 +922,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,17</t>
+          <t>0,04; 0,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,21</t>
+          <t>0,1; 0,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,18</t>
+          <t>0,08; 0,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,19</t>
+          <t>0,07; 0,17</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,13</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,24</t>
+          <t>0,31</t>
         </is>
       </c>
     </row>
@@ -1012,32 +1012,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,67</t>
+          <t>0,35; 0,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,58</t>
+          <t>0,31; 0,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,18</t>
+          <t>0,04; 0,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,14</t>
+          <t>0,05; 0,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,23</t>
+          <t>0,09; 0,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,32</t>
+          <t>0,18; 0,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,34</t>
+          <t>0,22; 0,45</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,26</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,68</t>
+          <t>0,32; 0,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1127,37 +1127,37 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,66</t>
+          <t>0,31; 0,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,04</t>
+          <t>0,0; 0,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,16</t>
+          <t>0,02; 0,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,1</t>
+          <t>0,03; 0,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,35</t>
+          <t>0,16; 0,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,25</t>
+          <t>0,09; 0,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,36</t>
+          <t>0,17; 0,36</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,24</t>
+          <t>0,22</t>
         </is>
       </c>
     </row>
@@ -1227,22 +1227,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,59</t>
+          <t>0,24; 0,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,45</t>
+          <t>0,18; 0,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,57</t>
+          <t>0,22; 0,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,18</t>
+          <t>0,03; 0,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,23</t>
+          <t>0,04; 0,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,33</t>
+          <t>0,14; 0,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,34</t>
+          <t>0,15; 0,32</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>0,18</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,27</t>
+          <t>0,31</t>
         </is>
       </c>
     </row>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,53</t>
+          <t>0,32; 0,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,59</t>
+          <t>0,34; 0,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1357,12 +1357,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,17</t>
+          <t>0,06; 0,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,22</t>
+          <t>0,12; 0,25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,36</t>
+          <t>0,25; 0,38</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,35</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,39</t>
+          <t>0,23; 0,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,29</t>
+          <t>0,17; 0,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,68</t>
+          <t>0,52; 0,76</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,08</t>
+          <t>0,02; 0,08</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,21</t>
+          <t>0,12; 0,2</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,38</t>
+          <t>0,29; 0,42</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,24</t>
+          <t>0,26</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,47</t>
+          <t>0,38; 0,49</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,11</t>
+          <t>0,08; 0,12</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1592,12 +1592,12 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,23</t>
+          <t>0,18; 0,22</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,28</t>
+          <t>0,23; 0,29</t>
         </is>
       </c>
     </row>
